--- a/preview/TSLA/TSLA_financials.xlsx
+++ b/preview/TSLA/TSLA_financials.xlsx
@@ -9425,7 +9425,7 @@
       <c r="F95" s="266" t="n"/>
       <c r="G95" s="266" t="n"/>
       <c r="H95" s="266" t="n">
-        <v>388.64</v>
+        <v>386.94</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1">
@@ -9551,7 +9551,7 @@
       <c r="F100" s="266" t="n"/>
       <c r="G100" s="266" t="n"/>
       <c r="H100" s="266" t="n">
-        <v>0.0432</v>
+        <v>0.0433</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1">
@@ -10053,7 +10053,7 @@
       <c r="C126" s="2" t="n"/>
       <c r="D126" s="25" t="inlineStr">
         <is>
-          <t>Confiance IA : 58%</t>
+          <t>Confiance IA : 62%</t>
         </is>
       </c>
       <c r="E126" s="25" t="n"/>
@@ -10095,7 +10095,7 @@
       <c r="B129" s="51" t="n"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Cible Bear : 280.0</t>
+          <t>Cible Bear : 310.0</t>
         </is>
       </c>
     </row>
@@ -10103,7 +10103,7 @@
       <c r="B130" s="51" t="n"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Tesla affiche une croissance revenue négative en 2025 mais bénéficie d'une marge brute solide et d'une position dominante sur l'IA/robotique. La valorisation reste élevée malgré un ralentissement du m</t>
+          <t xml:space="preserve">Tesla affiche des multiples de valorisation extrêmes malgré une croissance revenue en repli et des marges sous pression. Le modèle intégré (véhicules, énergie, IA) reste disruptif mais la concurrence </t>
         </is>
       </c>
     </row>
@@ -10111,7 +10111,7 @@
       <c r="B131" s="51" t="n"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Invalidation : Récession, concurrence accrue ou retards technologiques majeurs</t>
+          <t>Invalidation : Récession macro + baisse subventions &gt;30% + rappel Autopilot &gt;2Md$</t>
         </is>
       </c>
     </row>
@@ -10406,7 +10406,7 @@
         </is>
       </c>
       <c r="C14" s="536" t="n">
-        <v>388.69</v>
+        <v>386.93</v>
       </c>
     </row>
     <row r="15">
@@ -20301,7 +20301,7 @@
         </is>
       </c>
       <c r="D9" s="477" t="n">
-        <v>76.95999999999999</v>
+        <v>76.91</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>175174.81</v>
@@ -20342,7 +20342,7 @@
         </is>
       </c>
       <c r="D10" s="477" t="n">
-        <v>11.74</v>
+        <v>11.72</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>184568.38</v>

--- a/preview/TSLA/TSLA_financials.xlsx
+++ b/preview/TSLA/TSLA_financials.xlsx
@@ -14924,7 +14924,7 @@
         <v>226</v>
       </c>
       <c r="H95" s="238" t="n">
-        <v>376.71</v>
+        <v>375.03</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1">
@@ -15056,7 +15056,7 @@
       <c r="F100" s="458" t="n"/>
       <c r="G100" s="458" t="n"/>
       <c r="H100" s="459" t="n">
-        <v>0.0433</v>
+        <v>0.0432</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1">
@@ -15192,7 +15192,7 @@
       <c r="F106" s="458" t="n"/>
       <c r="G106" s="458" t="n"/>
       <c r="H106" s="459" t="n">
-        <v>0.9943</v>
+        <v>0.9942</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1">
@@ -15212,7 +15212,7 @@
       <c r="F107" s="458" t="n"/>
       <c r="G107" s="458" t="n"/>
       <c r="H107" s="459" t="n">
-        <v>0.0057</v>
+        <v>0.0058</v>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1">
@@ -15913,7 +15913,7 @@
         </is>
       </c>
       <c r="C15" s="573" t="n">
-        <v>376.71</v>
+        <v>374.99</v>
       </c>
     </row>
     <row r="17">
@@ -26029,7 +26029,7 @@
         </is>
       </c>
       <c r="D9" s="542" t="n">
-        <v>75.3</v>
+        <v>75.03</v>
       </c>
       <c r="E9" s="476" t="n">
         <v>173303.61</v>
@@ -26069,7 +26069,7 @@
         </is>
       </c>
       <c r="D10" s="542" t="n">
-        <v>11.61</v>
+        <v>11.63</v>
       </c>
       <c r="E10" s="476" t="n">
         <v>183371.55</v>
@@ -26189,7 +26189,7 @@
         </is>
       </c>
       <c r="D13" s="543" t="n">
-        <v>87.84</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="E13" s="479" t="n">
         <v>258704.92</v>

--- a/preview/TSLA/TSLA_financials.xlsx
+++ b/preview/TSLA/TSLA_financials.xlsx
@@ -24333,7 +24333,7 @@
         </is>
       </c>
       <c r="D12" s="588" t="n">
-        <v>78.23999999999999</v>
+        <v>82.42</v>
       </c>
       <c r="E12" s="589" t="n">
         <v>144555.72</v>
@@ -24373,7 +24373,7 @@
         </is>
       </c>
       <c r="D13" s="591" t="n">
-        <v>85.66</v>
+        <v>91.14</v>
       </c>
       <c r="E13" s="592" t="n">
         <v>258333.95</v>

--- a/preview/TSLA/TSLA_financials.xlsx
+++ b/preview/TSLA/TSLA_financials.xlsx
@@ -13226,7 +13226,7 @@
       <c r="F100" s="426" t="n"/>
       <c r="G100" s="426" t="n"/>
       <c r="H100" s="427" t="n">
-        <v>0.0434</v>
+        <v>0.0429</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1">
@@ -24216,7 +24216,7 @@
         <v>76.73999999999999</v>
       </c>
       <c r="E9" s="589" t="n">
-        <v>173303.61</v>
+        <v>175328.49</v>
       </c>
       <c r="F9" s="589" t="n">
         <v>185019.01</v>
@@ -24373,10 +24373,10 @@
         </is>
       </c>
       <c r="D13" s="591" t="n">
-        <v>88.95999999999999</v>
+        <v>88.84</v>
       </c>
       <c r="E13" s="592" t="n">
-        <v>258704.92</v>
+        <v>260840.42</v>
       </c>
       <c r="F13" s="592" t="n">
         <v>321913</v>
